--- a/Team-Data/2014-15/4-2-2014-15.xlsx
+++ b/Team-Data/2014-15/4-2-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -814,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-0.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
         <v>12</v>
@@ -969,7 +1036,7 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -984,7 +1051,7 @@
         <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>19</v>
@@ -1154,7 +1221,7 @@
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1530,10 +1597,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K7" t="n">
         <v>0.459</v>
@@ -1598,16 +1665,16 @@
         <v>9.9</v>
       </c>
       <c r="M7" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0.757</v>
@@ -1616,7 +1683,7 @@
         <v>11.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>42.9</v>
@@ -1628,13 +1695,13 @@
         <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
         <v>4.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z7" t="n">
         <v>18.4</v>
@@ -1643,16 +1710,16 @@
         <v>20.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>103.5</v>
+        <v>103.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1661,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1679,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1715,16 +1782,16 @@
         <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -1771,46 +1838,46 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O8" t="n">
         <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R8" t="n">
         <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
         <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.5</v>
@@ -1819,19 +1886,19 @@
         <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB8" t="n">
         <v>104.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1867,7 +1934,7 @@
         <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
         <v>17</v>
@@ -1876,7 +1943,7 @@
         <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>24</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2031,7 +2098,7 @@
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2052,13 +2119,13 @@
         <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.827</v>
+        <v>0.824</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.478</v>
@@ -2332,22 +2399,22 @@
         <v>0.397</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P11" t="n">
         <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.772</v>
+        <v>0.773</v>
       </c>
       <c r="R11" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S11" t="n">
         <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
         <v>27.4</v>
@@ -2368,16 +2435,16 @@
         <v>19.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.7</v>
+        <v>109.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2395,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2410,16 +2477,16 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
@@ -2437,7 +2504,7 @@
         <v>4</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -2511,40 +2578,40 @@
         <v>33.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
         <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="R12" t="n">
         <v>11.9</v>
       </c>
       <c r="S12" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>22.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W12" t="n">
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
         <v>22.1</v>
@@ -2556,10 +2623,10 @@
         <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>3</v>
@@ -2589,22 +2656,22 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR12" t="n">
         <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
         <v>15</v>
@@ -2622,19 +2689,19 @@
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>21</v>
@@ -2771,7 +2838,7 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
@@ -2780,7 +2847,7 @@
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>23</v>
@@ -2807,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3027,61 +3094,61 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="H15" t="n">
         <v>48.7</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P15" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T15" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="W15" t="n">
         <v>7.3</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3135,16 +3202,16 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
@@ -3153,7 +3220,7 @@
         <v>14</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
         <v>20</v>
@@ -3171,10 +3238,10 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
         <v>9</v>
@@ -3344,13 +3411,13 @@
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>0.453</v>
+        <v>0.459</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3427,13 +3494,13 @@
         <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R17" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S17" t="n">
         <v>29.8</v>
@@ -3442,7 +3509,7 @@
         <v>38.8</v>
       </c>
       <c r="U17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V17" t="n">
         <v>15</v>
@@ -3451,7 +3518,7 @@
         <v>8.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y17" t="n">
         <v>4.4</v>
@@ -3463,22 +3530,22 @@
         <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
@@ -3499,7 +3566,7 @@
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3523,13 +3590,13 @@
         <v>29</v>
       </c>
       <c r="AV17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX17" t="n">
         <v>22</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>6</v>
@@ -3899,7 +3966,7 @@
         <v>27</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.534</v>
+        <v>0.541</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
         <v>7.1</v>
@@ -3967,55 +4034,55 @@
         <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U20" t="n">
         <v>22.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z20" t="n">
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4030,10 +4097,10 @@
         <v>23</v>
       </c>
       <c r="AI20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>7</v>
@@ -4051,10 +4118,10 @@
         <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
@@ -4063,7 +4130,7 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
@@ -4433,7 +4500,7 @@
         <v>24</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -4483,55 +4550,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.297</v>
+        <v>0.293</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P23" t="n">
         <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R23" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41.3</v>
+        <v>41.5</v>
       </c>
       <c r="U23" t="n">
         <v>20.8</v>
@@ -4543,10 +4610,10 @@
         <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21</v>
@@ -4555,13 +4622,13 @@
         <v>18</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4579,10 +4646,10 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4600,19 +4667,19 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,10 +4691,10 @@
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4873,7 @@
         <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J25" t="n">
         <v>86.2</v>
@@ -4874,37 +4941,37 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O25" t="n">
         <v>16.5</v>
       </c>
       <c r="P25" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R25" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T25" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U25" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>4.7</v>
@@ -4916,16 +4983,16 @@
         <v>21.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4955,7 +5022,7 @@
         <v>9</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO25" t="n">
         <v>20</v>
@@ -4964,16 +5031,16 @@
         <v>23</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>27</v>
@@ -4982,7 +5049,7 @@
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4994,7 +5061,7 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5183,7 @@
         <v>5</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
@@ -5170,7 +5237,7 @@
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.649</v>
+        <v>0.653</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
@@ -5411,34 +5478,34 @@
         <v>38.7</v>
       </c>
       <c r="J28" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0.778</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
         <v>43.7</v>
@@ -5447,7 +5514,7 @@
         <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W28" t="n">
         <v>8</v>
@@ -5468,13 +5535,13 @@
         <v>102.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF28" t="n">
         <v>5</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
@@ -5668,13 +5735,13 @@
         <v>14</v>
       </c>
       <c r="AI29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5689,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5701,7 +5768,7 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU29" t="n">
         <v>21</v>
@@ -5713,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5728,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5865,16 +5932,16 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>4</v>
@@ -5895,16 +5962,16 @@
         <v>18</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ30" t="n">
         <v>11</v>
       </c>
       <c r="BA30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6050,7 +6117,7 @@
         <v>9</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>21</v>
@@ -6071,7 +6138,7 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
@@ -6083,7 +6150,7 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2014-15</t>
+          <t>2015-04-02</t>
         </is>
       </c>
     </row>
